--- a/docs/insumos/banco-v3-directivo.xlsx
+++ b/docs/insumos/banco-v3-directivo.xlsx
@@ -505,7 +505,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>85 preguntas · 347 opciones · 71 campos de caso · 32 rangos · 3 pares de consistencia.</t>
+          <t>85 preguntas · 347 opciones · 119 campos de caso · 32 rangos · 3 pares de consistencia.</t>
         </is>
       </c>
     </row>
@@ -982,9 +982,13 @@
       </c>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I15" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Un indicador sin denominador no es indicador: ese campo es inválido y arrastra al numerador.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -1278,9 +1282,13 @@
       </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I25" s="7" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Regla especial: cero reuniones con agenda previa y acta → el ítem puntúa 0 aunque declare 5 reuniones.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -1309,9 +1317,13 @@
       </c>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I26" s="7" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Detector de apagaincendios — corrección automática. Además del puntaje por campos válidos: índice = suma por cada problema de [campo 4 = «todos los meses» o «todas las semanas» → −1 · campo 5 = «nada, se resolvió» → −1 · campo 5 = «cambié el procedimiento» o «agregué un punto de control» → +1]. Índice ≤ −3: puntaje del ítem 0 y bandera de perfil reactivo / apagaincendios crónico. Índice −2 a 0: puntaje según campos válidos. Índice ≥ +2: puntaje del ítem 3, máximo directo.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -2862,9 +2874,13 @@
       </c>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I79" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>Regla especial: el puntaje cuenta solo las iniciativas con «implementada = sí o parcial». Tres ideas y cero implementadas = 0. Ideas vivas hoy = campo válido doble.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -9742,7 +9758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9890,7 +9906,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Nombre (texto ≤ 40 car.)</t>
+          <t>Indicador 1 · Nombre (texto ≤ 40 car.)</t>
         </is>
       </c>
       <c r="C12" s="7" t="n"/>
@@ -9903,7 +9919,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Numerador (texto)</t>
+          <t>Indicador 1 · Numerador (texto)</t>
         </is>
       </c>
       <c r="C13" s="7" t="n"/>
@@ -9916,7 +9932,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Denominador (texto)</t>
+          <t>Indicador 1 · Denominador (texto)</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -9929,7 +9945,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Meta (número)</t>
+          <t>Indicador 1 · Meta (número)</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -9942,7 +9958,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Resultado real del último mes (número)</t>
+          <t>Indicador 1 · Resultado real del último mes (número)</t>
         </is>
       </c>
       <c r="C16" s="7" t="n"/>
@@ -9955,7 +9971,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Frecuencia de revisión (tiempo real / diaria / semanal / quincenal / mensual) Un indicador sin denominador no es indicador: ese campo es inválido y arrastra al numerador.</t>
+          <t>Indicador 1 · Frecuencia de revisión (tiempo real / diaria / semanal / quincenal / mensual) Un indicador sin denominador no es indicador: ese campo es inválido y arrastra al numerador.</t>
         </is>
       </c>
       <c r="C17" s="7" t="n"/>
@@ -9963,12 +9979,12 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>¿Cuánto tardaste en enterarte? (mismo día / esa semana / al cierre del mes / cuando ya reclamó un cliente o gerencia)</t>
+          <t>Indicador 2 · Nombre (texto ≤ 40 car.)</t>
         </is>
       </c>
       <c r="C18" s="7" t="n"/>
@@ -9976,12 +9992,12 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>¿Cómo te enteraste? (por el dato / por un reporte del equipo / por un tercero / por el cliente / por mi jefe)</t>
+          <t>Indicador 2 · Numerador (texto)</t>
         </is>
       </c>
       <c r="C19" s="7" t="n"/>
@@ -9989,12 +10005,12 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>¿Qué cambiaste en tu sistema de control? (nada / hablé con el responsable / agregué un indicador / cambié la frecuencia de revisión / cambié a un soporte con dato en tiempo real / agregué un punto de control en el proceso / cambié a la persona)</t>
+          <t>Indicador 2 · Denominador (texto)</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -10002,12 +10018,12 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>¿Volvió a ocurrir? (sí / no / no lo sé)</t>
+          <t>Indicador 2 · Meta (número)</t>
         </is>
       </c>
       <c r="C21" s="7" t="n"/>
@@ -10015,12 +10031,12 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Dato o señal que lo anticipó (texto ≤ 40 car.)</t>
+          <t>Indicador 2 · Resultado real del último mes (número)</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -10028,12 +10044,12 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>¿Dónde lo viste? (lista)</t>
+          <t>Indicador 2 · Frecuencia de revisión (tiempo real / diaria / semanal / quincenal / mensual) Un indicador sin denominador no es indicador: ese campo es inválido y arrastra al numerador.</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -10041,12 +10057,12 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Días de anticipación ___</t>
+          <t>Indicador 3 · Nombre (texto ≤ 40 car.)</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
@@ -10054,12 +10070,12 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Decisión tomada (lista de 8)</t>
+          <t>Indicador 3 · Numerador (texto)</t>
         </is>
       </c>
       <c r="C25" s="7" t="n"/>
@@ -10067,12 +10083,12 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Impacto evitado estimado (rango en soles o en días)</t>
+          <t>Indicador 3 · Denominador (texto)</t>
         </is>
       </c>
       <c r="C26" s="7" t="n"/>
@@ -10080,12 +10096,12 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Con quién (lista)</t>
+          <t>Indicador 3 · Meta (número)</t>
         </is>
       </c>
       <c r="C27" s="7" t="n"/>
@@ -10093,12 +10109,12 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Frecuencia (lista)</t>
+          <t>Indicador 3 · Resultado real del último mes (número)</t>
         </is>
       </c>
       <c r="C28" s="7" t="n"/>
@@ -10106,12 +10122,12 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Duración (lista)</t>
+          <t>Indicador 3 · Frecuencia de revisión (tiempo real / diaria / semanal / quincenal / mensual) Un indicador sin denominador no es indicador: ese campo es inválido y arrastra al numerador.</t>
         </is>
       </c>
       <c r="C29" s="7" t="n"/>
@@ -10119,12 +10135,12 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>¿Agenda enviada antes? (sí/no)</t>
+          <t>¿Cuánto tardaste en enterarte? (mismo día / esa semana / al cierre del mes / cuando ya reclamó un cliente o gerencia)</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -10132,12 +10148,12 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>¿Qué documento salía? (nada / notas personales / acta con acuerdos y responsables / registro en sistema) Regla especial: cero reuniones con agenda previa y acta → ítem puntúa 0 aunque declare 5 reuniones.</t>
+          <t>¿Cómo te enteraste? (por el dato / por un reporte del equipo / por un tercero / por el cliente / por mi jefe)</t>
         </is>
       </c>
       <c r="C31" s="7" t="n"/>
@@ -10145,12 +10161,12 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Descripción (texto ≤ 60 car.)</t>
+          <t>¿Qué cambiaste en tu sistema de control? (nada / hablé con el responsable / agregué un indicador / cambié la frecuencia de revisión / cambié a un soporte con dato en tiempo real / agregué un punto de control en el proceso / cambié a la persona)</t>
         </is>
       </c>
       <c r="C32" s="7" t="n"/>
@@ -10158,12 +10174,12 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>¿Era previsible? (sí, y no lo previne / sí, y falló la prevención que había / no, era imprevisible)</t>
+          <t>¿Volvió a ocurrir? (sí / no / no lo sé)</t>
         </is>
       </c>
       <c r="C33" s="7" t="n"/>
@@ -10171,12 +10187,12 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Origen (falla de una persona / falla del proceso / cliente o factor externo / decisión de otra área / falta de información a tiempo)</t>
+          <t>Dato o señal que lo anticipó (texto ≤ 40 car.)</t>
         </is>
       </c>
       <c r="C34" s="7" t="n"/>
@@ -10184,12 +10200,12 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>¿Con qué frecuencia ocurre? (primera vez / ha pasado antes este año / pasa todos los meses / pasa todas las semanas)</t>
+          <t>¿Dónde lo viste? (lista)</t>
         </is>
       </c>
       <c r="C35" s="7" t="n"/>
@@ -10197,12 +10213,12 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>¿Qué dejaste hecho para que no se repita? (nada, se resolvió / avisé a quien corresponde / cambié el procedimiento / agregué un punto de control / lo escalé)</t>
+          <t>Días de anticipación ___</t>
         </is>
       </c>
       <c r="C36" s="7" t="n"/>
@@ -10210,12 +10226,12 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>¿En qué fallaste al elegir? (me fié del CV / me fié de la entrevista / me presionó la urgencia por cubrir / no verifiqué referencias / evalué lo técnico y no lo actitudinal / no definí bien el perfil antes de buscar)</t>
+          <t>Decisión tomada (lista de 8)</t>
         </is>
       </c>
       <c r="C37" s="7" t="n"/>
@@ -10223,12 +10239,12 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>¿Cuánto tardaste en darte cuenta? (primera semana / primer mes / segundo o tercer mes / después de seis meses)</t>
+          <t>Impacto evitado estimado (rango en soles o en días)</t>
         </is>
       </c>
       <c r="C38" s="7" t="n"/>
@@ -10236,12 +10252,12 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Meses que duró en el puesto ___</t>
+          <t>Reunión 1 · Con quién (lista)</t>
         </is>
       </c>
       <c r="C39" s="7" t="n"/>
@@ -10249,12 +10265,12 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Costo estimado (rango en soles)</t>
+          <t>Reunión 1 · Frecuencia (lista)</t>
         </is>
       </c>
       <c r="C40" s="7" t="n"/>
@@ -10262,12 +10278,12 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>¿Qué cambiaste en tu forma de contratar? (nada / agregué prueba práctica / agregué verificación de referencias / cambié el perfil / involucré a más evaluadores / alargué el periodo de prueba / definí indicadores desde el día 1)</t>
+          <t>Reunión 1 · Duración (lista)</t>
         </is>
       </c>
       <c r="C41" s="7" t="n"/>
@@ -10275,12 +10291,12 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Indicador (texto ≤ 40 car.)</t>
+          <t>Reunión 1 · ¿Agenda enviada antes? (sí/no)</t>
         </is>
       </c>
       <c r="C42" s="7" t="n"/>
@@ -10288,12 +10304,12 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Valor antes ___</t>
+          <t>Reunión 1 · ¿Qué documento salía? (nada / notas personales / acta con acuerdos y responsables / registro en sistema)</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -10301,12 +10317,12 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Valor después ___</t>
+          <t>Reunión 2 · Con quién (lista)</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -10314,12 +10330,12 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Unidad (lista)</t>
+          <t>Reunión 2 · Frecuencia (lista)</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -10327,12 +10343,12 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Meses que tomó ___</t>
+          <t>Reunión 2 · Duración (lista)</t>
         </is>
       </c>
       <c r="C46" s="7" t="n"/>
@@ -10340,12 +10356,12 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Tu aporte específico (diseñé el plan / conseguí los recursos / cambié el proceso / cambié al equipo / ejecuté personalmente la parte crítica / coordiné a las áreas)</t>
+          <t>Reunión 2 · ¿Agenda enviada antes? (sí/no)</t>
         </is>
       </c>
       <c r="C47" s="7" t="n"/>
@@ -10353,12 +10369,12 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Quién puede confirmarlo (nombre + cargo + contacto) El último campo hace verificable todo el bloque. Sin él, el ítem puntúa la mitad.</t>
+          <t>Reunión 2 · ¿Qué documento salía? (nada / notas personales / acta con acuerdos y responsables / registro en sistema)</t>
         </is>
       </c>
       <c r="C48" s="7" t="n"/>
@@ -10366,12 +10382,12 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Nombre del proceso (texto ≤ 40 car.)</t>
+          <t>Reunión 3 · Con quién (lista)</t>
         </is>
       </c>
       <c r="C49" s="7" t="n"/>
@@ -10379,12 +10395,12 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>¿Existe documento? (no / instructivo / procedimiento con responsables / procedimiento en sistema)</t>
+          <t>Reunión 3 · Frecuencia (lista)</t>
         </is>
       </c>
       <c r="C50" s="7" t="n"/>
@@ -10392,12 +10408,12 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>¿Cuántas personas lo ejecutan hoy? ___</t>
+          <t>Reunión 3 · Duración (lista)</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -10405,12 +10421,12 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>¿Sigue operando? (sí / no / no lo sé)</t>
+          <t>Reunión 3 · ¿Agenda enviada antes? (sí/no)</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -10418,12 +10434,12 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Horas tuyas que liberó por semana ___</t>
+          <t>Reunión 3 · ¿Qué documento salía? (nada / notas personales / acta con acuerdos y responsables / registro en sistema)</t>
         </is>
       </c>
       <c r="C53" s="7" t="n"/>
@@ -10431,12 +10447,12 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>D41</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>¿Cuándo lo dejaste instalado? (mes/año) Si "¿Existe documento?" = "no", los seis campos se invalidan: no está escrito, no cuenta.</t>
+          <t>Reunión 4 · Con quién (lista)</t>
         </is>
       </c>
       <c r="C54" s="7" t="n"/>
@@ -10444,12 +10460,12 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>D42</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Qué proponías (texto ≤ 60 car.)</t>
+          <t>Reunión 4 · Frecuencia (lista)</t>
         </is>
       </c>
       <c r="C55" s="7" t="n"/>
@@ -10457,12 +10473,12 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>D42</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>¿Se implementó? (sí completa / sí parcial / no)</t>
+          <t>Reunión 4 · Duración (lista)</t>
         </is>
       </c>
       <c r="C56" s="7" t="n"/>
@@ -10470,12 +10486,12 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>D42</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Indicador que mejoró (texto ≤ 40 car.)</t>
+          <t>Reunión 4 · ¿Agenda enviada antes? (sí/no)</t>
         </is>
       </c>
       <c r="C57" s="7" t="n"/>
@@ -10483,12 +10499,12 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>D42</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Antes ___ Después ___</t>
+          <t>Reunión 4 · ¿Qué documento salía? (nada / notas personales / acta con acuerdos y responsables / registro en sistema)</t>
         </is>
       </c>
       <c r="C58" s="7" t="n"/>
@@ -10496,12 +10512,12 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>D42</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Días entre ver el problema y proponerlo (mismo día / esa semana / ese mes / más de un mes)</t>
+          <t>Reunión 5 · Con quién (lista)</t>
         </is>
       </c>
       <c r="C59" s="7" t="n"/>
@@ -10509,12 +10525,12 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>D54</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Hora en que despiertas ___</t>
+          <t>Reunión 5 · Frecuencia (lista)</t>
         </is>
       </c>
       <c r="C60" s="7" t="n"/>
@@ -10522,12 +10538,12 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>D54</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Hora en que empiezas a trabajar ___</t>
+          <t>Reunión 5 · Duración (lista)</t>
         </is>
       </c>
       <c r="C61" s="7" t="n"/>
@@ -10535,12 +10551,12 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>D54</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Hora en que cierras ___</t>
+          <t>Reunión 5 · ¿Agenda enviada antes? (sí/no)</t>
         </is>
       </c>
       <c r="C62" s="7" t="n"/>
@@ -10548,12 +10564,12 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>D54</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Hora en que duermes ___</t>
+          <t>Reunión 5 · ¿Qué documento salía? (nada / notas personales / acta con acuerdos y responsables / registro en sistema)</t>
         </is>
       </c>
       <c r="C63" s="7" t="n"/>
@@ -10561,12 +10577,12 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>D54</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>¿Cuántas veces revisas trabajo después de cerrar? (ninguna / 1 / 2–3 / todo el tiempo) Validación: si "hora en que cierras" y "hora en que duermes" son la misma → campo inválido + bandera de sostenibilidad.</t>
+          <t>Problema 1 · Descripción (texto ≤ 60 car.)</t>
         </is>
       </c>
       <c r="C64" s="7" t="n"/>
@@ -10574,12 +10590,12 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>D72</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Qué hiciste (texto ≤ 60 car.)</t>
+          <t>Problema 1 · ¿Era previsible? (sí, y no lo previne / sí, y falló la prevención que había / no, era imprevisible)</t>
         </is>
       </c>
       <c r="C65" s="7" t="n"/>
@@ -10587,12 +10603,12 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>D72</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Cuándo (esta semana / este mes / este año / no recuerdo)</t>
+          <t>Problema 1 · Origen (falla de una persona / falla del proceso / cliente o factor externo / decisión de otra área / falta de información a tiempo)</t>
         </is>
       </c>
       <c r="C66" s="7" t="n"/>
@@ -10600,12 +10616,12 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>D72</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Tiempo que te tomó (&lt; 1 h / medio día / un día / más)</t>
+          <t>Problema 1 · ¿Con qué frecuencia ocurre? (primera vez / ha pasado antes este año / pasa todos los meses / pasa todas las semanas)</t>
         </is>
       </c>
       <c r="C67" s="7" t="n"/>
@@ -10613,12 +10629,12 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>D72</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>¿Alguien se enteró? (sí / no) "No recuerdo" en el campo 2 invalida el ítem completo.</t>
+          <t>Problema 1 · ¿Qué dejaste hecho para que no se repita? (nada, se resolvió / avisé a quien corresponde / cambié el procedimiento / agregué un punto de control / lo escalé)</t>
         </is>
       </c>
       <c r="C68" s="7" t="n"/>
@@ -10626,12 +10642,12 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>D74</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Qué exigías (texto ≤ 60 car.)</t>
+          <t>Problema 2 · Descripción (texto ≤ 60 car.)</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -10639,12 +10655,12 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>D74</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>¿Cómo se medía? (no se medía, era criterio / checklist de verificación / indicador numérico con meta / auditoría periódica / certificación externa)</t>
+          <t>Problema 2 · ¿Era previsible? (sí, y no lo previne / sí, y falló la prevención que había / no, era imprevisible)</t>
         </is>
       </c>
       <c r="C70" s="7" t="n"/>
@@ -10652,12 +10668,12 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>D74</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>¿Qué pasaba si no se cumplía? (nada / se corregía / no se entregaba hasta cumplir / había consecuencia formal)</t>
+          <t>Problema 2 · Origen (falla de una persona / falla del proceso / cliente o factor externo / decisión de otra área / falta de información a tiempo)</t>
         </is>
       </c>
       <c r="C71" s="7" t="n"/>
@@ -10665,12 +10681,12 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>D74</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>% de cumplimiento alcanzado ___ "No se medía, era criterio" invalida ese campo: un estándar sin medición no es estándar. C-Iniciativa</t>
+          <t>Problema 2 · ¿Con qué frecuencia ocurre? (primera vez / ha pasado antes este año / pasa todos los meses / pasa todas las semanas)</t>
         </is>
       </c>
       <c r="C72" s="7" t="n"/>
@@ -10678,12 +10694,12 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>D75</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Qué era (texto ≤ 40 car.)</t>
+          <t>Problema 2 · ¿Qué dejaste hecho para que no se repita? (nada, se resolvió / avisé a quien corresponde / cambié el procedimiento / agregué un punto de control / lo escalé)</t>
         </is>
       </c>
       <c r="C73" s="7" t="n"/>
@@ -10691,12 +10707,12 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>D75</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>¿Llegó a implementarse? (sí / parcial / no)</t>
+          <t>Problema 3 · Descripción (texto ≤ 60 car.)</t>
         </is>
       </c>
       <c r="C74" s="7" t="n"/>
@@ -10704,15 +10720,639 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Problema 3 · ¿Era previsible? (sí, y no lo previne / sí, y falló la prevención que había / no, era imprevisible)</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Problema 3 · Origen (falla de una persona / falla del proceso / cliente o factor externo / decisión de otra área / falta de información a tiempo)</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Problema 3 · ¿Con qué frecuencia ocurre? (primera vez / ha pasado antes este año / pasa todos los meses / pasa todas las semanas)</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Problema 3 · ¿Qué dejaste hecho para que no se repita? (nada, se resolvió / avisé a quien corresponde / cambié el procedimiento / agregué un punto de control / lo escalé)</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>D34</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>¿En qué fallaste al elegir? (me fié del CV / me fié de la entrevista / me presionó la urgencia por cubrir / no verifiqué referencias / evalué lo técnico y no lo actitudinal / no definí bien el perfil antes de buscar)</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>D34</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>¿Cuánto tardaste en darte cuenta? (primera semana / primer mes / segundo o tercer mes / después de seis meses)</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>D34</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Meses que duró en el puesto ___</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>D34</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Costo estimado (rango en soles)</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>D34</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>¿Qué cambiaste en tu forma de contratar? (nada / agregué prueba práctica / agregué verificación de referencias / cambié el perfil / involucré a más evaluadores / alargué el periodo de prueba / definí indicadores desde el día 1)</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>D36</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Indicador (texto ≤ 40 car.)</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>D36</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Valor antes ___</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>D36</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Valor después ___</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>D36</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Unidad (lista)</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>D36</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Meses que tomó ___</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>D36</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Tu aporte específico (diseñé el plan / conseguí los recursos / cambié el proceso / cambié al equipo / ejecuté personalmente la parte crítica / coordiné a las áreas)</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>D36</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Quién puede confirmarlo (nombre + cargo + contacto) El último campo hace verificable todo el bloque. Sin él, el ítem puntúa la mitad.</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>D41</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Nombre del proceso (texto ≤ 40 car.)</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>D41</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>¿Existe documento? (no / instructivo / procedimiento con responsables / procedimiento en sistema)</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>D41</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>¿Cuántas personas lo ejecutan hoy? ___</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>D41</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>¿Sigue operando? (sí / no / no lo sé)</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>D41</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Horas tuyas que liberó por semana ___</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>D41</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>¿Cuándo lo dejaste instalado? (mes/año) Si "¿Existe documento?" = "no", los seis campos se invalidan: no está escrito, no cuenta.</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>D42</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Qué proponías (texto ≤ 60 car.)</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>D42</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>¿Se implementó? (sí completa / sí parcial / no)</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>D42</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Indicador que mejoró (texto ≤ 40 car.)</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>D42</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Antes ___ Después ___</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>D42</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Días entre ver el problema y proponerlo (mismo día / esa semana / ese mes / más de un mes)</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>D54</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Hora en que despiertas ___</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>D54</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>Hora en que empiezas a trabajar ___</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>D54</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Hora en que cierras ___</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>D54</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Hora en que duermes ___</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>D54</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>¿Cuántas veces revisas trabajo después de cerrar? (ninguna / 1 / 2–3 / todo el tiempo) Validación: si "hora en que cierras" y "hora en que duermes" son la misma → campo inválido + bandera de sostenibilidad.</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>D72</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Qué hiciste (texto ≤ 60 car.)</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>D72</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Cuándo (esta semana / este mes / este año / no recuerdo)</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>D72</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Tiempo que te tomó (&lt; 1 h / medio día / un día / más)</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>D72</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>¿Alguien se enteró? (sí / no) "No recuerdo" en el campo 2 invalida el ítem completo.</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>D74</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>Qué exigías (texto ≤ 60 car.)</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>D74</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>¿Cómo se medía? (no se medía, era criterio / checklist de verificación / indicador numérico con meta / auditoría periódica / certificación externa)</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>D74</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>¿Qué pasaba si no se cumplía? (nada / se corregía / no se entregaba hasta cumplir / había consecuencia formal)</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>D74</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>% de cumplimiento alcanzado ___ "No se medía, era criterio" invalida ese campo: un estándar sin medición no es estándar. C-Iniciativa</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
           <t>D75</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>¿Sigue viva hoy? (sí / no / no lo sé) Regla especial: el puntaje cuenta solo las iniciativas con "implementada = sí o parcial". Tres ideas y cero implementadas = 0. Ideas vivas hoy = campo válido doble.</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="n"/>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 1 · Qué era (texto ≤ 40 car.)</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 1 · ¿Llegó a implementarse? (sí / parcial / no)</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 1 · ¿Sigue viva hoy? (sí / no / no lo sé)</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 2 · Qué era (texto ≤ 40 car.)</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 2 · ¿Llegó a implementarse? (sí / parcial / no)</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 2 · ¿Sigue viva hoy? (sí / no / no lo sé)</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 3 · Qué era (texto ≤ 40 car.)</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 3 · ¿Llegó a implementarse? (sí / parcial / no)</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>D75</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 3 · ¿Sigue viva hoy? (sí / no / no lo sé)</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/insumos/banco-v3-directivo.xlsx
+++ b/docs/insumos/banco-v3-directivo.xlsx
@@ -4668,7 +4668,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Seguimiento diario documentado Opción Clave</t>
+          <t>Seguimiento diario documentado</t>
         </is>
       </c>
       <c r="C78" s="7" t="n">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>El reporte de indicadores del área Opción Clave</t>
+          <t>El reporte de indicadores del área</t>
         </is>
       </c>
       <c r="C104" s="7" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>Cuál encaja mejor con la forma de trabajo del equipo Opción Valor</t>
+          <t>Cuál encaja mejor con la forma de trabajo del equipo</t>
         </is>
       </c>
       <c r="C160" s="7" t="n"/>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="B186" s="7" t="inlineStr">
         <is>
-          <t>Recalcular qué parte de la meta sigue siendo alcanzable y comunicarlo hoy Opción Clave</t>
+          <t>Recalcular qué parte de la meta sigue siendo alcanzable y comunicarlo hoy</t>
         </is>
       </c>
       <c r="C186" s="7" t="n">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="B320" s="7" t="inlineStr">
         <is>
-          <t>Hace más de un año Opción Valor</t>
+          <t>Hace más de un año</t>
         </is>
       </c>
       <c r="C320" s="7" t="n"/>

--- a/docs/insumos/banco-v3-directivo.xlsx
+++ b/docs/insumos/banco-v3-directivo.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -560,6 +560,8 @@
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -569,6 +571,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -615,6 +618,16 @@
           <t>Nota interna (opcional)</t>
         </is>
       </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Fórmula de puntaje (solo V)</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Usa los rangos de (solo V)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -660,6 +673,16 @@
       <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Guía para el evaluador. El candidato nunca la ve.</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Si el ítem V no se puntúa por tramos: la fórmula, en palabras.</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Si el ítem V usa la tabla de otra pregunta: su código.</t>
         </is>
       </c>
     </row>
